--- a/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-SV.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-SV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46DA3B2-0759-46C9-A786-6E204D715DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647BEA7F-6966-4F45-BEA3-74659577E723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,24 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>MSSV</t>
   </si>
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>DH24TIN06</t>
-  </si>
-  <si>
-    <t>Cong nghe thong tin</t>
-  </si>
-  <si>
-    <t>vana@student.edu.vn</t>
-  </si>
-  <si>
-    <t>0901234567</t>
   </si>
   <si>
     <t>STT</t>
@@ -59,22 +47,46 @@
     <t>DANH SÁCH SINH VIÊN THỰC TẬP</t>
   </si>
   <si>
-    <t>Họ</t>
+    <t>Công nghệ thông tin</t>
   </si>
   <si>
-    <t>Tên</t>
+    <t>Khoa</t>
   </si>
   <si>
-    <t>Nguyen Van</t>
+    <t>honganh170421@gmail.com</t>
   </si>
   <si>
-    <t>A</t>
+    <t>Phạm Thị Hồng Anh</t>
+  </si>
+  <si>
+    <t>C23A.TH1</t>
+  </si>
+  <si>
+    <t>Công nghệ phần mềm</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>C#, .NET Core, SQL Server</t>
+  </si>
+  <si>
+    <t>0901234567</t>
+  </si>
+  <si>
+    <t>Họ Tên</t>
   </si>
   <si>
     <t>Lớp</t>
   </si>
   <si>
     <t>Ngành</t>
+  </si>
+  <si>
+    <t>Nguyện Vọng</t>
+  </si>
+  <si>
+    <t>Kỹ Năng</t>
   </si>
   <si>
     <t>SĐT</t>
@@ -84,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -116,6 +128,11 @@
       <family val="1"/>
       <charset val="163"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -161,6 +178,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -466,86 +488,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <f>IF(B3="","",1)</f>
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>2421160052</v>
+        <v>2421160001</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="str">
         <f>IF(B4="","",A3+1)</f>
         <v/>
@@ -555,10 +593,12 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="str">
         <f t="shared" ref="A5:A68" si="0">IF(B5="","",A4+1)</f>
         <v/>
@@ -568,10 +608,12 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -581,10 +623,12 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -594,10 +638,12 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -607,10 +653,12 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -620,10 +668,12 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -633,10 +683,12 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -646,10 +698,12 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -659,10 +713,12 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -672,10 +728,12 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -685,10 +743,12 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -698,10 +758,12 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -711,10 +773,12 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -724,10 +788,12 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -737,10 +803,12 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -750,10 +818,12 @@
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -763,10 +833,12 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -776,10 +848,12 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -789,10 +863,12 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -802,10 +878,12 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -815,10 +893,12 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -828,10 +908,12 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -841,10 +923,12 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -854,10 +938,12 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -867,10 +953,12 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -880,10 +968,12 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -893,10 +983,12 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -906,10 +998,12 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -919,10 +1013,12 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -932,10 +1028,12 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -945,10 +1043,12 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -958,10 +1058,12 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -971,10 +1073,12 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -984,10 +1088,12 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -997,10 +1103,12 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1010,10 +1118,12 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1023,10 +1133,12 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1036,10 +1148,12 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1049,10 +1163,12 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1062,10 +1178,12 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1075,10 +1193,12 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1088,10 +1208,12 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1101,10 +1223,12 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1114,10 +1238,12 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1127,10 +1253,12 @@
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1140,10 +1268,12 @@
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1153,10 +1283,12 @@
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1166,10 +1298,12 @@
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1179,10 +1313,12 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1192,10 +1328,12 @@
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1205,10 +1343,12 @@
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1218,10 +1358,12 @@
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1231,10 +1373,12 @@
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1244,10 +1388,12 @@
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1257,10 +1403,12 @@
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1270,10 +1418,12 @@
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1283,10 +1433,12 @@
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1296,10 +1448,12 @@
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1309,10 +1463,12 @@
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1322,10 +1478,12 @@
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1335,10 +1493,12 @@
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1348,10 +1508,12 @@
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1361,10 +1523,12 @@
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1374,10 +1538,12 @@
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1387,10 +1553,12 @@
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="str">
         <f t="shared" ref="A69:A94" si="1">IF(B69="","",A68+1)</f>
         <v/>
@@ -1400,10 +1568,12 @@
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1413,10 +1583,12 @@
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1426,10 +1598,12 @@
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1439,10 +1613,12 @@
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1452,10 +1628,12 @@
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1465,10 +1643,12 @@
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1478,10 +1658,12 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1491,10 +1673,12 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1504,10 +1688,12 @@
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1517,10 +1703,12 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1530,10 +1718,12 @@
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1543,10 +1733,12 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1556,10 +1748,12 @@
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1569,10 +1763,12 @@
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1582,10 +1778,12 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1595,10 +1793,12 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1608,10 +1808,12 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1621,10 +1823,12 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1634,10 +1838,12 @@
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1647,10 +1853,12 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1660,10 +1868,12 @@
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1673,10 +1883,12 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1686,10 +1898,12 @@
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1699,10 +1913,12 @@
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1712,10 +1928,12 @@
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1725,13 +1943,16 @@
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>